--- a/omicron/xlsx/850-FDR-test-plan.xlsx
+++ b/omicron/xlsx/850-FDR-test-plan.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>generated 2026-09-05 12:27 from 850.html</t>
+          <t>generated 2026-09-15 01:10 from src/850-fdr.html</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>Faulted phase collapsed, 6.0 ×CT applied. The fault is still there on every reclose.</t>
+          <t>Faulted phase collapsed, 6 ×CT applied. The fault is still there on every reclose.</t>
         </is>
       </c>
       <c r="H3" s="12" t="n">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Faulted phase collapsed, 6.0 ×CT applied. The fault is still there on every reclose.</t>
+          <t>Faulted phase collapsed, 6 ×CT applied. The fault is still there on every reclose.</t>
         </is>
       </c>
       <c r="H5" s="12" t="n">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>19.534@0.0</t>
+          <t>39.769@-60.6</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>19.534@180.0</t>
+          <t>39.769@-119.4</t>
         </is>
       </c>
       <c r="N22" s="15" t="n"/>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="L23" s="15" t="inlineStr">
         <is>
-          <t>23.875@0.0</t>
+          <t>42.071@-55.4</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>23.875@180.0</t>
+          <t>42.071@-124.6</t>
         </is>
       </c>
       <c r="N23" s="15" t="n"/>
@@ -3172,12 +3172,12 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>29.301@0.0</t>
+          <t>45.371@-49.8</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>29.301@180.0</t>
+          <t>45.371@-130.2</t>
         </is>
       </c>
       <c r="N24" s="15" t="n"/>
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L25" s="15" t="inlineStr">
         <is>
-          <t>35.812@0.0</t>
+          <t>49.825@-44.0</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>35.812@180.0</t>
+          <t>49.825@-136.0</t>
         </is>
       </c>
       <c r="N25" s="15" t="n"/>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>48.835@0.0</t>
+          <t>59.873@-35.4</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>48.835@180.0</t>
+          <t>59.873@-144.6</t>
         </is>
       </c>
       <c r="N26" s="15" t="n"/>
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L27" s="15" t="inlineStr">
         <is>
-          <t>59.687@0.0</t>
+          <t>69.011@-30.1</t>
         </is>
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>59.687@180.0</t>
+          <t>69.011@-149.9</t>
         </is>
       </c>
       <c r="N27" s="15" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F71" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.60× pickup</t>
+          <t>Timing at 0.6× pickup</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
@@ -22489,7 +22489,7 @@
         </is>
       </c>
       <c r="M123" s="15" t="n">
-        <v>19.534</v>
+        <v>39.769</v>
       </c>
       <c r="N123" s="15" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         </is>
       </c>
       <c r="O123" s="15" t="n">
-        <v>0</v>
+        <v>-60.58</v>
       </c>
       <c r="P123" s="15" t="n">
         <v>60</v>
@@ -22563,7 +22563,7 @@
         </is>
       </c>
       <c r="M124" s="15" t="n">
-        <v>19.534</v>
+        <v>39.769</v>
       </c>
       <c r="N124" s="15" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="O124" s="15" t="n">
-        <v>180</v>
+        <v>-119.42</v>
       </c>
       <c r="P124" s="15" t="n">
         <v>60</v>
@@ -22937,7 +22937,7 @@
         </is>
       </c>
       <c r="M129" s="15" t="n">
-        <v>23.875</v>
+        <v>42.071</v>
       </c>
       <c r="N129" s="15" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="O129" s="15" t="n">
-        <v>0</v>
+        <v>-55.43</v>
       </c>
       <c r="P129" s="15" t="n">
         <v>60</v>
@@ -23011,7 +23011,7 @@
         </is>
       </c>
       <c r="M130" s="15" t="n">
-        <v>23.875</v>
+        <v>42.071</v>
       </c>
       <c r="N130" s="15" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="O130" s="15" t="n">
-        <v>180</v>
+        <v>-124.57</v>
       </c>
       <c r="P130" s="15" t="n">
         <v>60</v>
@@ -23385,7 +23385,7 @@
         </is>
       </c>
       <c r="M135" s="15" t="n">
-        <v>29.301</v>
+        <v>45.371</v>
       </c>
       <c r="N135" s="15" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         </is>
       </c>
       <c r="O135" s="15" t="n">
-        <v>0</v>
+        <v>-49.77</v>
       </c>
       <c r="P135" s="15" t="n">
         <v>60</v>
@@ -23459,7 +23459,7 @@
         </is>
       </c>
       <c r="M136" s="15" t="n">
-        <v>29.301</v>
+        <v>45.371</v>
       </c>
       <c r="N136" s="15" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         </is>
       </c>
       <c r="O136" s="15" t="n">
-        <v>180</v>
+        <v>-130.23</v>
       </c>
       <c r="P136" s="15" t="n">
         <v>60</v>
@@ -23833,7 +23833,7 @@
         </is>
       </c>
       <c r="M141" s="15" t="n">
-        <v>35.812</v>
+        <v>49.825</v>
       </c>
       <c r="N141" s="15" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         </is>
       </c>
       <c r="O141" s="15" t="n">
-        <v>0</v>
+        <v>-44.05</v>
       </c>
       <c r="P141" s="15" t="n">
         <v>60</v>
@@ -23907,7 +23907,7 @@
         </is>
       </c>
       <c r="M142" s="15" t="n">
-        <v>35.812</v>
+        <v>49.825</v>
       </c>
       <c r="N142" s="15" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         </is>
       </c>
       <c r="O142" s="15" t="n">
-        <v>180</v>
+        <v>-135.95</v>
       </c>
       <c r="P142" s="15" t="n">
         <v>60</v>
@@ -24281,7 +24281,7 @@
         </is>
       </c>
       <c r="M147" s="15" t="n">
-        <v>48.835</v>
+        <v>59.873</v>
       </c>
       <c r="N147" s="15" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         </is>
       </c>
       <c r="O147" s="15" t="n">
-        <v>0</v>
+        <v>-35.35</v>
       </c>
       <c r="P147" s="15" t="n">
         <v>60</v>
@@ -24355,7 +24355,7 @@
         </is>
       </c>
       <c r="M148" s="15" t="n">
-        <v>48.835</v>
+        <v>59.873</v>
       </c>
       <c r="N148" s="15" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="O148" s="15" t="n">
-        <v>180</v>
+        <v>-144.65</v>
       </c>
       <c r="P148" s="15" t="n">
         <v>60</v>
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M153" s="15" t="n">
-        <v>59.687</v>
+        <v>69.011</v>
       </c>
       <c r="N153" s="15" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         </is>
       </c>
       <c r="O153" s="15" t="n">
-        <v>0</v>
+        <v>-30.13</v>
       </c>
       <c r="P153" s="15" t="n">
         <v>60</v>
@@ -24803,7 +24803,7 @@
         </is>
       </c>
       <c r="M154" s="15" t="n">
-        <v>59.687</v>
+        <v>69.011</v>
       </c>
       <c r="N154" s="15" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         </is>
       </c>
       <c r="O154" s="15" t="n">
-        <v>180</v>
+        <v>-149.87</v>
       </c>
       <c r="P154" s="15" t="n">
         <v>60</v>
@@ -29970,7 +29970,7 @@
       </c>
       <c r="G224" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H224" s="12" t="n"/>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H225" s="12" t="n"/>
@@ -30118,7 +30118,7 @@
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H226" s="12" t="n"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H227" s="12" t="n"/>
@@ -30266,7 +30266,7 @@
       </c>
       <c r="G228" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H228" s="12" t="n"/>
@@ -30340,7 +30340,7 @@
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H229" s="12" t="n"/>
@@ -31302,7 +31302,7 @@
       </c>
       <c r="G242" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H242" s="15" t="n"/>
@@ -31376,7 +31376,7 @@
       </c>
       <c r="G243" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H243" s="15" t="n"/>
@@ -31450,7 +31450,7 @@
       </c>
       <c r="G244" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H244" s="15" t="n"/>
@@ -31524,7 +31524,7 @@
       </c>
       <c r="G245" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H245" s="15" t="n"/>
@@ -31598,7 +31598,7 @@
       </c>
       <c r="G246" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H246" s="15" t="n"/>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H247" s="15" t="n"/>
@@ -31746,7 +31746,7 @@
       </c>
       <c r="G248" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H248" s="15" t="n"/>
@@ -31820,7 +31820,7 @@
       </c>
       <c r="G249" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H249" s="15" t="n"/>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="G250" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H250" s="15" t="n"/>
@@ -31968,7 +31968,7 @@
       </c>
       <c r="G251" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H251" s="15" t="n"/>
@@ -32042,7 +32042,7 @@
       </c>
       <c r="G252" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H252" s="15" t="n"/>
@@ -32116,7 +32116,7 @@
       </c>
       <c r="G253" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H253" s="15" t="n"/>
@@ -32190,7 +32190,7 @@
       </c>
       <c r="G254" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H254" s="15" t="n"/>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="G255" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H255" s="15" t="n"/>
@@ -32338,7 +32338,7 @@
       </c>
       <c r="G256" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H256" s="15" t="n"/>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="G257" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H257" s="15" t="n"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="G258" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H258" s="15" t="n"/>
@@ -32560,7 +32560,7 @@
       </c>
       <c r="G259" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H259" s="15" t="n"/>
@@ -32634,7 +32634,7 @@
       </c>
       <c r="G260" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H260" s="15" t="n"/>
@@ -32708,7 +32708,7 @@
       </c>
       <c r="G261" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H261" s="15" t="n"/>
@@ -32782,7 +32782,7 @@
       </c>
       <c r="G262" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H262" s="15" t="n"/>
@@ -32856,7 +32856,7 @@
       </c>
       <c r="G263" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H263" s="15" t="n"/>
@@ -32930,7 +32930,7 @@
       </c>
       <c r="G264" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H264" s="15" t="n"/>
@@ -33004,7 +33004,7 @@
       </c>
       <c r="G265" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H265" s="15" t="n"/>
@@ -33326,7 +33326,11 @@
       <c r="P269" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q269" s="11" t="n"/>
+      <c r="Q269" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R269" s="11" t="inlineStr">
         <is>
           <t>OPERATE</t>
@@ -33770,7 +33774,11 @@
       <c r="P275" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q275" s="11" t="n"/>
+      <c r="Q275" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R275" s="11" t="inlineStr">
         <is>
           <t>RESTRAIN</t>
@@ -33966,7 +33974,7 @@
       </c>
       <c r="G278" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H278" s="12" t="n"/>
@@ -34040,7 +34048,7 @@
       </c>
       <c r="G279" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H279" s="12" t="n"/>
@@ -34114,7 +34122,7 @@
       </c>
       <c r="G280" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H280" s="12" t="n"/>
@@ -34188,7 +34196,7 @@
       </c>
       <c r="G281" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H281" s="12" t="n"/>
@@ -34214,7 +34222,11 @@
       <c r="P281" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q281" s="11" t="n"/>
+      <c r="Q281" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R281" s="11" t="inlineStr">
         <is>
           <t>0.020 s</t>
@@ -34262,7 +34274,7 @@
       </c>
       <c r="G282" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H282" s="12" t="n"/>
@@ -34336,7 +34348,7 @@
       </c>
       <c r="G283" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H283" s="12" t="n"/>
@@ -34658,7 +34670,11 @@
       <c r="P287" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q287" s="14" t="n"/>
+      <c r="Q287" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R287" s="14" t="inlineStr">
         <is>
           <t>OPERATE</t>
@@ -35102,7 +35118,11 @@
       <c r="P293" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q293" s="14" t="n"/>
+      <c r="Q293" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R293" s="14" t="inlineStr">
         <is>
           <t>RESTRAIN</t>
@@ -35298,7 +35318,7 @@
       </c>
       <c r="G296" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H296" s="15" t="n"/>
@@ -35372,7 +35392,7 @@
       </c>
       <c r="G297" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H297" s="15" t="n"/>
@@ -35446,7 +35466,7 @@
       </c>
       <c r="G298" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H298" s="15" t="n"/>
@@ -35520,7 +35540,7 @@
       </c>
       <c r="G299" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H299" s="15" t="n"/>
@@ -35546,7 +35566,11 @@
       <c r="P299" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q299" s="14" t="n"/>
+      <c r="Q299" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R299" s="14" t="inlineStr">
         <is>
           <t>1.406 s</t>
@@ -35594,7 +35618,7 @@
       </c>
       <c r="G300" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H300" s="15" t="n"/>
@@ -35668,7 +35692,7 @@
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H301" s="15" t="n"/>
@@ -35742,7 +35766,7 @@
       </c>
       <c r="G302" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H302" s="15" t="n"/>
@@ -35816,7 +35840,7 @@
       </c>
       <c r="G303" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H303" s="15" t="n"/>
@@ -35890,7 +35914,7 @@
       </c>
       <c r="G304" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H304" s="15" t="n"/>
@@ -35964,7 +35988,7 @@
       </c>
       <c r="G305" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H305" s="15" t="n"/>
@@ -35990,7 +36014,11 @@
       <c r="P305" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q305" s="14" t="n"/>
+      <c r="Q305" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R305" s="14" t="inlineStr">
         <is>
           <t>0.588 s</t>
@@ -36038,7 +36066,7 @@
       </c>
       <c r="G306" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H306" s="15" t="n"/>
@@ -36112,7 +36140,7 @@
       </c>
       <c r="G307" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H307" s="15" t="n"/>
@@ -36186,7 +36214,7 @@
       </c>
       <c r="G308" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H308" s="15" t="n"/>
@@ -36260,7 +36288,7 @@
       </c>
       <c r="G309" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H309" s="15" t="n"/>
@@ -36334,7 +36362,7 @@
       </c>
       <c r="G310" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H310" s="15" t="n"/>
@@ -36408,7 +36436,7 @@
       </c>
       <c r="G311" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H311" s="15" t="n"/>
@@ -36434,7 +36462,11 @@
       <c r="P311" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q311" s="14" t="n"/>
+      <c r="Q311" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R311" s="14" t="inlineStr">
         <is>
           <t>0.262 s</t>
@@ -36482,7 +36514,7 @@
       </c>
       <c r="G312" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H312" s="15" t="n"/>
@@ -36556,7 +36588,7 @@
       </c>
       <c r="G313" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H313" s="15" t="n"/>
@@ -36630,7 +36662,7 @@
       </c>
       <c r="G314" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H314" s="15" t="n"/>
@@ -36704,7 +36736,7 @@
       </c>
       <c r="G315" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H315" s="15" t="n"/>
@@ -36778,7 +36810,7 @@
       </c>
       <c r="G316" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H316" s="15" t="n"/>
@@ -36852,7 +36884,7 @@
       </c>
       <c r="G317" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H317" s="15" t="n"/>
@@ -36878,7 +36910,11 @@
       <c r="P317" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q317" s="14" t="n"/>
+      <c r="Q317" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R317" s="14" t="inlineStr">
         <is>
           <t>0.138 s</t>
@@ -36926,7 +36962,7 @@
       </c>
       <c r="G318" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H318" s="15" t="n"/>
@@ -37000,7 +37036,7 @@
       </c>
       <c r="G319" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H319" s="15" t="n"/>
@@ -37962,7 +37998,7 @@
       </c>
       <c r="G332" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H332" s="12" t="n"/>
@@ -38036,7 +38072,7 @@
       </c>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H333" s="12" t="n"/>
@@ -38110,7 +38146,7 @@
       </c>
       <c r="G334" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H334" s="12" t="n"/>
@@ -38184,7 +38220,7 @@
       </c>
       <c r="G335" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H335" s="12" t="n"/>
@@ -38258,7 +38294,7 @@
       </c>
       <c r="G336" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H336" s="12" t="n"/>
@@ -38332,7 +38368,7 @@
       </c>
       <c r="G337" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H337" s="12" t="n"/>
@@ -39294,7 +39330,7 @@
       </c>
       <c r="G350" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H350" s="15" t="n"/>
@@ -39368,7 +39404,7 @@
       </c>
       <c r="G351" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H351" s="15" t="n"/>
@@ -39442,7 +39478,7 @@
       </c>
       <c r="G352" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H352" s="15" t="n"/>
@@ -39516,7 +39552,7 @@
       </c>
       <c r="G353" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H353" s="15" t="n"/>
@@ -39590,7 +39626,7 @@
       </c>
       <c r="G354" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H354" s="15" t="n"/>
@@ -39664,7 +39700,7 @@
       </c>
       <c r="G355" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H355" s="15" t="n"/>
@@ -39738,7 +39774,7 @@
       </c>
       <c r="G356" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H356" s="15" t="n"/>
@@ -39812,7 +39848,7 @@
       </c>
       <c r="G357" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H357" s="15" t="n"/>
@@ -39886,7 +39922,7 @@
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H358" s="15" t="n"/>
@@ -39960,7 +39996,7 @@
       </c>
       <c r="G359" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H359" s="15" t="n"/>
@@ -40034,7 +40070,7 @@
       </c>
       <c r="G360" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H360" s="15" t="n"/>
@@ -40108,7 +40144,7 @@
       </c>
       <c r="G361" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H361" s="15" t="n"/>
@@ -40182,7 +40218,7 @@
       </c>
       <c r="G362" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H362" s="15" t="n"/>
@@ -40256,7 +40292,7 @@
       </c>
       <c r="G363" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H363" s="15" t="n"/>
@@ -40330,7 +40366,7 @@
       </c>
       <c r="G364" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H364" s="15" t="n"/>
@@ -40404,7 +40440,7 @@
       </c>
       <c r="G365" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H365" s="15" t="n"/>
@@ -40478,7 +40514,7 @@
       </c>
       <c r="G366" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H366" s="15" t="n"/>
@@ -40552,7 +40588,7 @@
       </c>
       <c r="G367" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H367" s="15" t="n"/>
@@ -40626,7 +40662,7 @@
       </c>
       <c r="G368" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H368" s="15" t="n"/>
@@ -40700,7 +40736,7 @@
       </c>
       <c r="G369" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H369" s="15" t="n"/>
@@ -40774,7 +40810,7 @@
       </c>
       <c r="G370" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H370" s="15" t="n"/>
@@ -40848,7 +40884,7 @@
       </c>
       <c r="G371" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H371" s="15" t="n"/>
@@ -40922,7 +40958,7 @@
       </c>
       <c r="G372" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H372" s="15" t="n"/>
@@ -40996,7 +41032,7 @@
       </c>
       <c r="G373" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H373" s="15" t="n"/>
@@ -41318,7 +41354,11 @@
       <c r="P377" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q377" s="11" t="n"/>
+      <c r="Q377" s="11" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R377" s="11" t="inlineStr">
         <is>
           <t>OPERATE</t>
@@ -41762,7 +41802,11 @@
       <c r="P383" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q383" s="11" t="n"/>
+      <c r="Q383" s="11" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R383" s="11" t="inlineStr">
         <is>
           <t>RESTRAIN</t>
@@ -41958,7 +42002,7 @@
       </c>
       <c r="G386" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H386" s="12" t="n"/>
@@ -42032,7 +42076,7 @@
       </c>
       <c r="G387" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H387" s="12" t="n"/>
@@ -42106,7 +42150,7 @@
       </c>
       <c r="G388" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H388" s="12" t="n"/>
@@ -42180,7 +42224,7 @@
       </c>
       <c r="G389" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H389" s="12" t="n"/>
@@ -42206,7 +42250,11 @@
       <c r="P389" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q389" s="11" t="n"/>
+      <c r="Q389" s="11" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R389" s="11" t="inlineStr">
         <is>
           <t>0.020 s</t>
@@ -42254,7 +42302,7 @@
       </c>
       <c r="G390" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H390" s="12" t="n"/>
@@ -42328,7 +42376,7 @@
       </c>
       <c r="G391" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H391" s="12" t="n"/>
@@ -42650,7 +42698,11 @@
       <c r="P395" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q395" s="14" t="n"/>
+      <c r="Q395" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R395" s="14" t="inlineStr">
         <is>
           <t>OPERATE</t>
@@ -43094,7 +43146,11 @@
       <c r="P401" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q401" s="14" t="n"/>
+      <c r="Q401" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R401" s="14" t="inlineStr">
         <is>
           <t>RESTRAIN</t>
@@ -43290,7 +43346,7 @@
       </c>
       <c r="G404" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H404" s="15" t="n"/>
@@ -43364,7 +43420,7 @@
       </c>
       <c r="G405" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H405" s="15" t="n"/>
@@ -43438,7 +43494,7 @@
       </c>
       <c r="G406" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H406" s="15" t="n"/>
@@ -43512,7 +43568,7 @@
       </c>
       <c r="G407" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H407" s="15" t="n"/>
@@ -43538,7 +43594,11 @@
       <c r="P407" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q407" s="14" t="n"/>
+      <c r="Q407" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R407" s="14" t="inlineStr">
         <is>
           <t>2.006 s</t>
@@ -43586,7 +43646,7 @@
       </c>
       <c r="G408" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H408" s="15" t="n"/>
@@ -43660,7 +43720,7 @@
       </c>
       <c r="G409" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H409" s="15" t="n"/>
@@ -43734,7 +43794,7 @@
       </c>
       <c r="G410" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H410" s="15" t="n"/>
@@ -43808,7 +43868,7 @@
       </c>
       <c r="G411" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H411" s="15" t="n"/>
@@ -43882,7 +43942,7 @@
       </c>
       <c r="G412" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H412" s="15" t="n"/>
@@ -43956,7 +44016,7 @@
       </c>
       <c r="G413" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H413" s="15" t="n"/>
@@ -43982,7 +44042,11 @@
       <c r="P413" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q413" s="14" t="n"/>
+      <c r="Q413" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R413" s="14" t="inlineStr">
         <is>
           <t>1.260 s</t>
@@ -44030,7 +44094,7 @@
       </c>
       <c r="G414" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H414" s="15" t="n"/>
@@ -44104,7 +44168,7 @@
       </c>
       <c r="G415" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H415" s="15" t="n"/>
@@ -44178,7 +44242,7 @@
       </c>
       <c r="G416" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H416" s="15" t="n"/>
@@ -44252,7 +44316,7 @@
       </c>
       <c r="G417" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H417" s="15" t="n"/>
@@ -44326,7 +44390,7 @@
       </c>
       <c r="G418" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H418" s="15" t="n"/>
@@ -44400,7 +44464,7 @@
       </c>
       <c r="G419" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H419" s="15" t="n"/>
@@ -44426,7 +44490,11 @@
       <c r="P419" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q419" s="14" t="n"/>
+      <c r="Q419" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R419" s="14" t="inlineStr">
         <is>
           <t>0.856 s</t>
@@ -44474,7 +44542,7 @@
       </c>
       <c r="G420" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H420" s="15" t="n"/>
@@ -44548,7 +44616,7 @@
       </c>
       <c r="G421" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H421" s="15" t="n"/>
@@ -44622,7 +44690,7 @@
       </c>
       <c r="G422" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H422" s="15" t="n"/>
@@ -44696,7 +44764,7 @@
       </c>
       <c r="G423" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H423" s="15" t="n"/>
@@ -44770,7 +44838,7 @@
       </c>
       <c r="G424" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H424" s="15" t="n"/>
@@ -44844,7 +44912,7 @@
       </c>
       <c r="G425" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H425" s="15" t="n"/>
@@ -44870,7 +44938,11 @@
       <c r="P425" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q425" s="14" t="n"/>
+      <c r="Q425" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R425" s="14" t="inlineStr">
         <is>
           <t>0.594 s</t>
@@ -44918,7 +44990,7 @@
       </c>
       <c r="G426" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H426" s="15" t="n"/>
@@ -44992,7 +45064,7 @@
       </c>
       <c r="G427" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H427" s="15" t="n"/>
@@ -45954,7 +46026,7 @@
       </c>
       <c r="G440" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H440" s="12" t="n"/>
@@ -46028,7 +46100,7 @@
       </c>
       <c r="G441" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H441" s="12" t="n"/>
@@ -46102,7 +46174,7 @@
       </c>
       <c r="G442" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H442" s="12" t="n"/>
@@ -46176,7 +46248,7 @@
       </c>
       <c r="G443" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H443" s="12" t="n"/>
@@ -46250,7 +46322,7 @@
       </c>
       <c r="G444" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H444" s="12" t="n"/>
@@ -46324,7 +46396,7 @@
       </c>
       <c r="G445" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H445" s="12" t="n"/>
@@ -47286,7 +47358,7 @@
       </c>
       <c r="G458" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H458" s="15" t="n"/>
@@ -47360,7 +47432,7 @@
       </c>
       <c r="G459" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H459" s="15" t="n"/>
@@ -47434,7 +47506,7 @@
       </c>
       <c r="G460" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H460" s="15" t="n"/>
@@ -47508,7 +47580,7 @@
       </c>
       <c r="G461" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H461" s="15" t="n"/>
@@ -47582,7 +47654,7 @@
       </c>
       <c r="G462" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H462" s="15" t="n"/>
@@ -47656,7 +47728,7 @@
       </c>
       <c r="G463" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H463" s="15" t="n"/>
@@ -47730,7 +47802,7 @@
       </c>
       <c r="G464" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H464" s="15" t="n"/>
@@ -47804,7 +47876,7 @@
       </c>
       <c r="G465" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H465" s="15" t="n"/>
@@ -47878,7 +47950,7 @@
       </c>
       <c r="G466" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H466" s="15" t="n"/>
@@ -47952,7 +48024,7 @@
       </c>
       <c r="G467" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H467" s="15" t="n"/>
@@ -48026,7 +48098,7 @@
       </c>
       <c r="G468" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H468" s="15" t="n"/>
@@ -48100,7 +48172,7 @@
       </c>
       <c r="G469" s="14" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H469" s="15" t="n"/>
@@ -48174,7 +48246,7 @@
       </c>
       <c r="G470" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H470" s="15" t="n"/>
@@ -48248,7 +48320,7 @@
       </c>
       <c r="G471" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H471" s="15" t="n"/>
@@ -48322,7 +48394,7 @@
       </c>
       <c r="G472" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H472" s="15" t="n"/>
@@ -48396,7 +48468,7 @@
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H473" s="15" t="n"/>
@@ -48470,7 +48542,7 @@
       </c>
       <c r="G474" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H474" s="15" t="n"/>
@@ -48544,7 +48616,7 @@
       </c>
       <c r="G475" s="14" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H475" s="15" t="n"/>
@@ -48618,7 +48690,7 @@
       </c>
       <c r="G476" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H476" s="15" t="n"/>
@@ -48692,7 +48764,7 @@
       </c>
       <c r="G477" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H477" s="15" t="n"/>
@@ -48766,7 +48838,7 @@
       </c>
       <c r="G478" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H478" s="15" t="n"/>
@@ -48840,7 +48912,7 @@
       </c>
       <c r="G479" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H479" s="15" t="n"/>
@@ -48914,7 +48986,7 @@
       </c>
       <c r="G480" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H480" s="15" t="n"/>
@@ -48988,7 +49060,7 @@
       </c>
       <c r="G481" s="14" t="inlineStr">
         <is>
-          <t>Timing at 10.0× pickup</t>
+          <t>Timing at 10× pickup</t>
         </is>
       </c>
       <c r="H481" s="15" t="n"/>
@@ -57522,7 +57594,7 @@
       </c>
       <c r="G596" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.60× pickup</t>
+          <t>Timing at 0.6× pickup</t>
         </is>
       </c>
       <c r="H596" s="12" t="n"/>
@@ -57600,7 +57672,7 @@
       </c>
       <c r="G597" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.60× pickup</t>
+          <t>Timing at 0.6× pickup</t>
         </is>
       </c>
       <c r="H597" s="12" t="n"/>
@@ -57674,7 +57746,7 @@
       </c>
       <c r="G598" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.60× pickup</t>
+          <t>Timing at 0.6× pickup</t>
         </is>
       </c>
       <c r="H598" s="12" t="n"/>
@@ -57748,7 +57820,7 @@
       </c>
       <c r="G599" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.60× pickup</t>
+          <t>Timing at 0.6× pickup</t>
         </is>
       </c>
       <c r="H599" s="12" t="n"/>
@@ -57822,7 +57894,7 @@
       </c>
       <c r="G600" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.60× pickup</t>
+          <t>Timing at 0.6× pickup</t>
         </is>
       </c>
       <c r="H600" s="12" t="n"/>
@@ -57896,7 +57968,7 @@
       </c>
       <c r="G601" s="11" t="inlineStr">
         <is>
-          <t>Timing at 0.60× pickup</t>
+          <t>Timing at 0.6× pickup</t>
         </is>
       </c>
       <c r="H601" s="12" t="n"/>
